--- a/keywords_master.xlsx
+++ b/keywords_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Claude\Bank Flow\Bank Flow\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA3B78D-5FFD-4553-8C76-EF09E015EB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B67186-26CD-4086-A22A-286A2FD77BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0542C7DC-9D21-4066-854D-98A9A3AD831F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4483" uniqueCount="812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4495" uniqueCount="815">
   <si>
     <t>Payment/Receipt</t>
   </si>
@@ -2475,6 +2475,15 @@
   </si>
   <si>
     <t>Investment</t>
+  </si>
+  <si>
+    <t>CKSPLNAPS</t>
+  </si>
+  <si>
+    <t>CKVPLNAPS</t>
+  </si>
+  <si>
+    <t>TAX RECOVERY</t>
   </si>
 </sst>
 </file>
@@ -2555,16 +2564,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -17871,42 +17889,77 @@
       </c>
     </row>
     <row r="749" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D749" s="3"/>
-      <c r="F749" s="3"/>
+      <c r="A749" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C749" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D749" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E749" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F749" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="750" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D750" s="3"/>
-      <c r="F750" s="3"/>
+      <c r="A750" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C750" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D750" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E750" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F750" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="751" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A751" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="B751" s="2" t="s">
-        <v>798</v>
+      <c r="A751" t="s">
+        <v>814</v>
+      </c>
+      <c r="B751" t="s">
+        <v>814</v>
       </c>
       <c r="C751" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D751" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E751" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F751" s="2" t="s">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F751" xr:uid="{82CB14E5-D4A6-4ED5-B79B-021FC3C27C57}"/>
-  <conditionalFormatting sqref="B36 A1:A750 B43:B741 B744:B745 A752:A1048576 A751:B751">
+  <conditionalFormatting sqref="A749:B749 B36 A1:A748 B43:B741 B744:B745 A750:A1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38">
     <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B38">
+  <conditionalFormatting sqref="B742:B743">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B742:B743">
+  <conditionalFormatting sqref="B750">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/keywords_master.xlsx
+++ b/keywords_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Claude\Bank Flow\Bank Flow\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B67186-26CD-4086-A22A-286A2FD77BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC60316-064F-4377-A472-4B7FA5FDBB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0542C7DC-9D21-4066-854D-98A9A3AD831F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$752</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4495" uniqueCount="815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4518" uniqueCount="820">
   <si>
     <t>Payment/Receipt</t>
   </si>
@@ -2484,6 +2484,21 @@
   </si>
   <si>
     <t>TAX RECOVERY</t>
+  </si>
+  <si>
+    <t>TD INT</t>
+  </si>
+  <si>
+    <t>CKSPLREMB</t>
+  </si>
+  <si>
+    <t>CKVPLREMB</t>
+  </si>
+  <si>
+    <t>CKSPLHOREMB</t>
+  </si>
+  <si>
+    <t>CKVPLHOREMB</t>
   </si>
 </sst>
 </file>
@@ -2943,7 +2958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82CB14E5-D4A6-4ED5-B79B-021FC3C27C57}">
-  <dimension ref="A1:F751"/>
+  <dimension ref="A1:F755"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -17948,9 +17963,86 @@
         <v>4</v>
       </c>
     </row>
+    <row r="752" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B752" t="s">
+        <v>815</v>
+      </c>
+      <c r="C752" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D752" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E752" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="F752" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A753" t="s">
+        <v>816</v>
+      </c>
+      <c r="B753" t="s">
+        <v>817</v>
+      </c>
+      <c r="C753" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D753" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E753" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F753" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A754" t="s">
+        <v>818</v>
+      </c>
+      <c r="B754" t="s">
+        <v>819</v>
+      </c>
+      <c r="C754" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D754" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="E754" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F754" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A755" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="C755" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D755" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="E755" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="F755" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F751" xr:uid="{82CB14E5-D4A6-4ED5-B79B-021FC3C27C57}"/>
-  <conditionalFormatting sqref="A749:B749 B36 A1:A748 B43:B741 B744:B745 A750:A1048576">
+  <autoFilter ref="A1:F752" xr:uid="{82CB14E5-D4A6-4ED5-B79B-021FC3C27C57}"/>
+  <conditionalFormatting sqref="A749:B749 B36 A1:A748 B43:B741 B744:B745 A750:A754 A756:A1048576 A755:B755">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38">
